--- a/_data/PLCTags_FG04.xlsx
+++ b/_data/PLCTags_FG04.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="R6f0b1ef591a34004"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="Rd4bb7253a02047a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC Tags" sheetId="1" r:id="Ra393ea9b04844211"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R9ff478e1a3da4936"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
   <x:si>
     <x:t xml:space="preserve">Name</x:t>
   </x:si>
@@ -63,6 +63,18 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">%Q401.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG04_Y_AxisZ_HomePos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%Q401.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FG04_Y_AxisZ_InHome</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">%I401.0</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BelongsToUnit</x:t>
@@ -218,6 +230,70 @@
         <x:v>14</x:v>
       </x:c>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -230,10 +306,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
